--- a/data/raw/Copa_2026_2027/aggregate/aggregated_game_stats_with_defense.xlsx
+++ b/data/raw/Copa_2026_2027/aggregate/aggregated_game_stats_with_defense.xlsx
@@ -733,7 +733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CE PALAMOS CAN PACO</t>
+          <t>U.E. CLARET A</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -812,7 +812,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U.E. CLARET A</t>
+          <t>CE PALAMOS CAN PACO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1049,38 +1049,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U.E. GAUDI-FORUS SARDENYA A</t>
+          <t>CANXAM&amp;PA - AECAM</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>83.86</v>
+        <v>93.48</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>78.7</v>
+        <v>80.23</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>89.43000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45.76271186440678</v>
+        <v>42.02898550724638</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35.6</v>
+        <v>30.8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2033898305084746</v>
+        <v>0.2463768115942029</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>30</v>
@@ -1089,77 +1089,77 @@
         <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T8" s="2" t="n">
         <v>15</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>40</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>40</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>40</v>
+        <v>26.66666666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CANXAM&amp;PA - AECAM</t>
+          <t>U.E. GAUDI-FORUS SARDENYA A</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>92.98</v>
+        <v>83.86</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>78.51000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>63.45</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>41.17647058823529</v>
+        <v>45.76271186440678</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>31.07</v>
+        <v>35.6</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2033898305084746</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>30</v>
@@ -1168,40 +1168,40 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>4</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T9" s="2" t="n">
         <v>15</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>43.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>40</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>26.66666666666667</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -1527,13 +1527,13 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>92.98</v>
+        <v>93.48</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>63.45</v>
+        <v>63.12</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>78.51000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>30.88235294117647</v>
@@ -11203,7 +11203,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>#0 Guillem Bao Oliveras</t>
+          <t>#2 Jordi Poch Campabadal</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -11213,22 +11213,22 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
@@ -11249,13 +11249,13 @@
         <v>1</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>0</v>
@@ -11264,124 +11264,124 @@
         <v>0</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AL2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM2" s="2" t="n">
+        <v>58.13953488372093</v>
+      </c>
+      <c r="AN2" s="2" t="n">
+        <v>0.900900900900901</v>
+      </c>
+      <c r="AO2" s="2" t="n">
+        <v>22.52252252252253</v>
+      </c>
+      <c r="AP2" s="2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AQ2" s="2" t="n">
+        <v>11.47131200068356</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="2" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AU2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW2" s="2" t="n">
         <v>100</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>08:17</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL2" s="2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="AM2" s="2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="AN2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="2" t="n">
-        <v>22.6276300293626</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT2" s="2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="AU2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AV2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>#1 Niels Geers Escalona</t>
+          <t>#3 Sowkin Shetty</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -11396,34 +11396,34 @@
         <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X3" s="2" t="n">
         <v>0</v>
@@ -11435,13 +11435,13 @@
         <v>0</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD3" s="2" t="n">
         <v>0</v>
@@ -11453,63 +11453,63 @@
         <v>0</v>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AL3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>00:48</t>
-        </is>
-      </c>
-      <c r="AK3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" s="2" t="n">
-        <v>150</v>
-      </c>
       <c r="AM3" s="2" t="n">
-        <v>150</v>
+        <v>86.63366336633663</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>3</v>
+        <v>1.541850220264317</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>0</v>
+        <v>11.01321585903084</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>58.57256314892297</v>
+        <v>18.33524216571782</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AV3" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AW3" s="2" t="n">
-        <v>0</v>
+        <v>57.14285714285714</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>#2 Genís Cabello Albert</t>
+          <t>#4 Sergi Carrasco Leon</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -11522,13 +11522,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -11549,10 +11549,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>0</v>
@@ -11561,7 +11561,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>0</v>
@@ -11573,7 +11573,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" s="2" t="n">
         <v>0</v>
@@ -11609,18 +11609,18 @@
         <v>0</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>01:39</t>
         </is>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="2" t="n">
         <v>0</v>
@@ -11632,16 +11632,16 @@
         <v>0</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="AP4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>16.00464723613835</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -11662,7 +11662,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#3 Dan Giner Falgueras</t>
+          <t>#5 Hector Gimenez Anton</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -11675,13 +11675,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
@@ -11702,10 +11702,10 @@
         <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>2</v>
@@ -11714,7 +11714,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W5" s="2" t="n">
         <v>0</v>
@@ -11762,18 +11762,18 @@
         <v>0</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL5" s="2" t="n">
         <v>0</v>
@@ -11785,16 +11785,16 @@
         <v>0</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>15.00791653637884</v>
+        <v>21.34537325725043</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -11815,32 +11815,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>#4 Bernat Bao Oliveras</t>
+          <t>#6 Marti Gomez Garcia</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -11861,28 +11861,28 @@
         <v>1</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X6" s="2" t="n">
         <v>0</v>
@@ -11894,100 +11894,100 @@
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AD6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
-      <c r="AK6" s="2" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AL6" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AM6" s="2" t="n">
-        <v>45.95588235294117</v>
-      </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.8417508417508417</v>
-      </c>
-      <c r="AO6" s="2" t="n">
-        <v>8.417508417508417</v>
-      </c>
       <c r="AP6" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>27.33258462360216</v>
+        <v>6.727667148737345</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#6 Franc Juanola Aguila</t>
+          <t>#7 Adria Torroja Corbella</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
@@ -12008,25 +12008,25 @@
         <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>1</v>
@@ -12047,13 +12047,13 @@
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD7" s="2" t="n">
         <v>0</v>
@@ -12065,54 +12065,54 @@
         <v>0</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>31:09</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>16.66666666666666</v>
+        <v>43.75</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>16.66666666666666</v>
+        <v>43.75</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="AP7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>9.025627708341261</v>
+        <v>24.43736039241657</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>16.66666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>0</v>
@@ -12121,32 +12121,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#7 Jose López Martínez</t>
+          <t>#9 Armak Karimi Gonzalez</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0</v>
@@ -12161,10 +12161,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>1</v>
@@ -12173,96 +12173,96 @@
         <v>0</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="AL8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="2" t="n">
+        <v>14.79289940828402</v>
+      </c>
+      <c r="AN8" s="2" t="n">
+        <v>0.2958579881656805</v>
+      </c>
+      <c r="AO8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AQ8" s="2" t="n">
+        <v>14.84129894175092</v>
+      </c>
+      <c r="AR8" t="n">
         <v>5</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="W8" s="2" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="X8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>23:34</t>
-        </is>
-      </c>
-      <c r="AK8" s="2" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="AL8" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM8" s="2" t="n">
-        <v>59.33544303797468</v>
-      </c>
-      <c r="AN8" s="2" t="n">
-        <v>1.099706744868035</v>
-      </c>
-      <c r="AO8" s="2" t="n">
-        <v>7.331378299120233</v>
-      </c>
-      <c r="AP8" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AQ8" s="2" t="n">
-        <v>27.12067082380683</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>10</v>
-      </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT8" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AU8" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AV8" s="2" t="n">
         <v>0</v>
@@ -12274,32 +12274,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>#9 Eduard Illa Martinez</t>
+          <t>#12 Oriol Aby Tascón Marquié</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0</v>
@@ -12326,7 +12326,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>0</v>
@@ -12338,7 +12338,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W9" s="2" t="n">
         <v>0</v>
@@ -12362,57 +12362,57 @@
         <v>0</v>
       </c>
       <c r="AD9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AG9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AI9" s="2" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AK9" s="2" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="AL9" s="2" t="n">
+        <v>68.18181818181817</v>
+      </c>
+      <c r="AM9" s="2" t="n">
+        <v>71.54882154882154</v>
+      </c>
+      <c r="AN9" s="2" t="n">
+        <v>1.430976430976431</v>
+      </c>
+      <c r="AO9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="2" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AQ9" s="2" t="n">
+        <v>35.25062558265051</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS9" t="n">
         <v>5</v>
       </c>
-      <c r="AL9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AN9" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="2" t="n">
-        <v>22.38441903780496</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1</v>
-      </c>
       <c r="AT9" s="2" t="n">
-        <v>20</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AU9" s="2" t="n">
         <v>0</v>
@@ -12421,191 +12421,191 @@
         <v>50</v>
       </c>
       <c r="AW9" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>#10 Xavi Maixenchs Bobe</t>
+          <t>#15 Albert Sitjes Lozano</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>29:34</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="AL10" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AM10" s="2" t="n">
+        <v>28.19548872180451</v>
+      </c>
+      <c r="AN10" s="2" t="n">
+        <v>0.5154639175257731</v>
+      </c>
+      <c r="AO10" s="2" t="n">
+        <v>8.59106529209622</v>
+      </c>
+      <c r="AP10" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ10" s="2" t="n">
+        <v>17.83385480663263</v>
+      </c>
+      <c r="AR10" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI10" s="2" t="n">
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU10" s="2" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="AV10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="2" t="n">
         <v>66.66666666666666</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>27:05</t>
-        </is>
-      </c>
-      <c r="AK10" s="2" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="AL10" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM10" s="2" t="n">
-        <v>66.25441696113073</v>
-      </c>
-      <c r="AN10" s="2" t="n">
-        <v>1.217532467532467</v>
-      </c>
-      <c r="AO10" s="2" t="n">
-        <v>8.116883116883116</v>
-      </c>
-      <c r="AP10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="2" t="n">
-        <v>21.3153667346136</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT10" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AU10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" s="2" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="AW10" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>#15 Joan Odena Massaguer</t>
+          <t>#44 Gonzalo Fernando Badal</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0</v>
@@ -12620,19 +12620,19 @@
         <v>0</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S11" s="2" t="n">
         <v>0</v>
@@ -12641,99 +12641,99 @@
         <v>2</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="W11" s="2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="X11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC11" s="2" t="n">
+      <c r="AD11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>30:50</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AL11" s="2" t="n">
         <v>66.66666666666666</v>
       </c>
-      <c r="AD11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI11" s="2" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>30:16</t>
-        </is>
-      </c>
-      <c r="AK11" s="2" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="AL11" s="2" t="n">
-        <v>53.57142857142857</v>
-      </c>
       <c r="AM11" s="2" t="n">
-        <v>53.93401015228426</v>
+        <v>66.96428571428572</v>
       </c>
       <c r="AN11" s="2" t="n">
-        <v>1.014319809069212</v>
+        <v>1.339285714285714</v>
       </c>
       <c r="AO11" s="2" t="n">
-        <v>5.966587112171839</v>
+        <v>0</v>
       </c>
       <c r="AP11" s="2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AQ11" s="2" t="n">
-        <v>25.94738744606032</v>
+        <v>16.4547828727604</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT11" s="2" t="n">
-        <v>50</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AU11" s="2" t="n">
-        <v>85.71428571428571</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AV11" s="2" t="n">
-        <v>14.28571428571428</v>
+        <v>0</v>
       </c>
       <c r="AW11" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>#17 Bru Postigo Camprubi</t>
+          <t>#77 Adrià Ordobàs Bengado</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -12743,22 +12743,22 @@
         <v>6</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -12785,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="S12" s="2" t="n">
         <v>0</v>
@@ -12794,13 +12794,13 @@
         <v>0</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="X12" s="2" t="n">
         <v>0</v>
@@ -12821,91 +12821,91 @@
         <v>0</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AG12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>50</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AK12" s="2" t="n">
-        <v>4.44</v>
+        <v>9</v>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>62.5</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AM12" s="2" t="n">
-        <v>67.56756756756756</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.5</v>
       </c>
       <c r="AO12" s="2" t="n">
-        <v>40.32258064516129</v>
+        <v>25</v>
       </c>
       <c r="AP12" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="2" t="n">
-        <v>17.8934420459738</v>
+        <v>38.96741975756112</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AS12" t="n">
         <v>2</v>
       </c>
       <c r="AT12" s="2" t="n">
-        <v>50</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AU12" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AV12" s="2" t="n">
-        <v>50</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AW12" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>#28 Iago Carbajo Aubeso</t>
+          <t>#87 Javier Vicente Nieto</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>0</v>
@@ -12932,28 +12932,28 @@
         <v>1</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X13" s="2" t="n">
         <v>0</v>
@@ -12974,63 +12974,63 @@
         <v>0</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI13" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AK13" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AL13" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM13" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN13" s="2" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="AO13" s="2" t="n">
-        <v>50</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="AP13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" s="2" t="n">
-        <v>7.831429056123406</v>
+        <v>20.45300815452256</v>
       </c>
       <c r="AR13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT13" s="2" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="AU13" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AV13" s="2" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AW13" s="2" t="n">
         <v>0</v>
@@ -15348,22 +15348,22 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>78.51000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>63.45</v>
+        <v>63.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>41.17647058823529</v>
+        <v>42.02898550724638</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30.48</v>
+        <v>30.345</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>46.93</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2463768115942029</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3</v>
@@ -15716,149 +15716,149 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CANXAM&amp;PA - AECAM</t>
+          <t>U.E. GAUDI-FORUS SARDENYA A</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>63.45</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>78.51000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>30.88235294117647</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+        <v>51.75438596491229</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>33.095</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>43.38</v>
+      </c>
       <c r="G8" s="2" t="n">
-        <v>0.25</v>
+        <v>0.2807017543859649</v>
       </c>
       <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="T8" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>60</v>
       </c>
       <c r="U8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>25</v>
+        <v>38.46153846153847</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U.E. GAUDI-FORUS SARDENYA A</t>
+          <t>CANXAM&amp;PA - AECAM</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>89.43000000000001</v>
+        <v>63.12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>78.7</v>
+        <v>80.23</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>51.75438596491229</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>33.095</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>43.38</v>
-      </c>
+        <v>30.88235294117647</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" s="2" t="n">
-        <v>0.2807017543859649</v>
+        <v>0.25</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J9" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>13</v>
-      </c>
       <c r="T9" s="2" t="n">
-        <v>60</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="U9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="W9" s="2" t="n">
-        <v>20</v>
-      </c>
       <c r="X9" s="2" t="n">
-        <v>38.46153846153847</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -16016,7 +16016,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>U.E. CLARET A</t>
+          <t>CE PALAMOS CAN PACO</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -16028,8 +16028,12 @@
       <c r="D12" s="2" t="n">
         <v>45.65217391304348</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" s="2" t="n">
+        <v>25.365</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>29.03</v>
+      </c>
       <c r="G12" s="2" t="n">
         <v>0.2318840579710145</v>
       </c>
@@ -16088,7 +16092,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CE PALAMOS CAN PACO</t>
+          <t>U.E. CLARET A</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -16100,12 +16104,8 @@
       <c r="D13" s="2" t="n">
         <v>51.51515151515152</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>25.365</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>29.03</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" s="2" t="n">
         <v>0.1060606060606061</v>
       </c>
@@ -20739,7 +20739,7 @@
         <v>0</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>16.03493477790279</v>
+        <v>15.86769515777448</v>
       </c>
       <c r="AR2" t="n">
         <v>4</v>
@@ -21045,7 +21045,7 @@
         <v>0</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>24.45687011232409</v>
+        <v>24.20179220126523</v>
       </c>
       <c r="AR4" t="n">
         <v>11</v>
@@ -21198,7 +21198,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>14.3800965603271</v>
+        <v>14.23011641263908</v>
       </c>
       <c r="AR5" t="n">
         <v>3</v>
@@ -21351,7 +21351,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>32.0504801317047</v>
+        <v>31.71620311739823</v>
       </c>
       <c r="AR6" t="n">
         <v>10</v>
@@ -21504,7 +21504,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>30.10880056698712</v>
+        <v>29.7947746954082</v>
       </c>
       <c r="AR7" t="n">
         <v>14</v>
@@ -21657,7 +21657,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="AQ8" s="2" t="n">
-        <v>20.11736227302009</v>
+        <v>19.90754414334737</v>
       </c>
       <c r="AR8" t="n">
         <v>9</v>
@@ -21688,13 +21688,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>3</v>
@@ -21733,7 +21733,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>0</v>
@@ -21792,37 +21792,37 @@
         </is>
       </c>
       <c r="AK9" s="2" t="n">
-        <v>10.88</v>
+        <v>11.88</v>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AM9" s="2" t="n">
-        <v>45.95588235294117</v>
+        <v>50.5050505050505</v>
       </c>
       <c r="AN9" s="2" t="n">
-        <v>0.9191176470588235</v>
+        <v>1.01010101010101</v>
       </c>
       <c r="AO9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AQ9" s="2" t="n">
-        <v>16.12248345519046</v>
+        <v>17.42072142022872</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT9" s="2" t="n">
-        <v>30</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AU9" s="2" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AV9" s="2" t="n">
         <v>37.5</v>
@@ -21963,7 +21963,7 @@
         <v>0</v>
       </c>
       <c r="AQ10" s="2" t="n">
-        <v>10.07773291320384</v>
+        <v>9.972625143979776</v>
       </c>
       <c r="AR10" t="n">
         <v>4</v>
@@ -22116,7 +22116,7 @@
         <v>0</v>
       </c>
       <c r="AQ11" s="2" t="n">
-        <v>17.99083187207799</v>
+        <v>17.80319282460116</v>
       </c>
       <c r="AR11" t="n">
         <v>1</v>
@@ -22269,7 +22269,7 @@
         <v>0</v>
       </c>
       <c r="AQ12" s="2" t="n">
-        <v>10.06436721968501</v>
+        <v>9.959398850685373</v>
       </c>
       <c r="AR12" t="n">
         <v>2</v>
@@ -26188,7 +26188,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>0</v>
@@ -28080,7 +28080,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>#2 Jordi Poch Campabadal</t>
+          <t>#0 Guillem Bao Oliveras</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -28090,22 +28090,22 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
@@ -28126,13 +28126,13 @@
         <v>1</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>0</v>
@@ -28141,13 +28141,13 @@
         <v>0</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>0</v>
@@ -28162,103 +28162,103 @@
         <v>0</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>50</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>58.13953488372093</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.900900900900901</v>
+        <v>1</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>22.52252252252253</v>
+        <v>25</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>11.47131200068356</v>
+        <v>22.6276300293626</v>
       </c>
       <c r="AR2" t="n">
         <v>3</v>
       </c>
       <c r="AS2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT2" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AV2" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AW2" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>#3 Sowkin Shetty</t>
+          <t>#1 Niels Geers Escalona</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -28273,120 +28273,120 @@
         <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="X3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>00:48</t>
         </is>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>8.08</v>
+        <v>1</v>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>86.63366336633663</v>
+        <v>150</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>1.541850220264317</v>
+        <v>3</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>11.01321585903084</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>18.33524216571782</v>
+        <v>58.57256314892297</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AU3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AV3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="AW3" s="2" t="n">
-        <v>57.14285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>#4 Sergi Carrasco Leon</t>
+          <t>#2 Genís Cabello Albert</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -28399,13 +28399,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>0</v>
@@ -28438,7 +28438,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>0</v>
@@ -28450,7 +28450,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="2" t="n">
         <v>0</v>
@@ -28486,18 +28486,18 @@
         <v>0</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>01:39</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL4" s="2" t="n">
         <v>0</v>
@@ -28509,16 +28509,16 @@
         <v>0</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AP4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0</v>
+        <v>16.00464723613835</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -28539,7 +28539,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#5 Hector Gimenez Anton</t>
+          <t>#3 Dan Giner Falgueras</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -28552,13 +28552,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
@@ -28579,10 +28579,10 @@
         <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>2</v>
@@ -28591,7 +28591,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>0</v>
@@ -28603,7 +28603,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W5" s="2" t="n">
         <v>0</v>
@@ -28639,18 +28639,18 @@
         <v>0</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL5" s="2" t="n">
         <v>0</v>
@@ -28662,16 +28662,16 @@
         <v>0</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>21.34537325725043</v>
+        <v>15.00791653637884</v>
       </c>
       <c r="AR5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -28692,32 +28692,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>#6 Marti Gomez Garcia</t>
+          <t>#4 Bernat Bao Oliveras</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -28738,28 +28738,28 @@
         <v>1</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X6" s="2" t="n">
         <v>0</v>
@@ -28771,100 +28771,100 @@
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>0</v>
+        <v>10.88</v>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>0</v>
+        <v>45.95588235294117</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0</v>
+        <v>0.8417508417508417</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>100</v>
+        <v>8.417508417508417</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>6.727667148737345</v>
+        <v>27.33258462360216</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AV6" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AW6" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#7 Adria Torroja Corbella</t>
+          <t>#6 Franc Juanola Aguila</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
@@ -28885,25 +28885,25 @@
         <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U7" s="2" t="n">
         <v>1</v>
@@ -28924,13 +28924,13 @@
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="2" t="n">
         <v>0</v>
@@ -28942,54 +28942,54 @@
         <v>0</v>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>31:09</t>
         </is>
       </c>
       <c r="AK7" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>43.75</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>43.75</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
       <c r="AP7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>24.43736039241657</v>
+        <v>9.025627708341261</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AT7" s="2" t="n">
-        <v>37.5</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="AU7" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AV7" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="AW7" s="2" t="n">
         <v>0</v>
@@ -28998,74 +28998,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#9 Armak Karimi Gonzalez</t>
+          <t>#7 Jose López Martínez</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="X8" s="2" t="n">
         <v>0</v>
@@ -29077,13 +29077,13 @@
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AD8" s="2" t="n">
         <v>0</v>
@@ -29098,48 +29098,48 @@
         <v>0</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AK8" s="2" t="n">
-        <v>6.76</v>
+        <v>12.64</v>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM8" s="2" t="n">
-        <v>14.79289940828402</v>
+        <v>59.33544303797468</v>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.2958579881656805</v>
+        <v>1.099706744868035</v>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>0</v>
+        <v>7.331378299120233</v>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AQ8" s="2" t="n">
-        <v>14.84129894175092</v>
+        <v>27.12067082380683</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT8" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU8" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AV8" s="2" t="n">
         <v>0</v>
@@ -29151,145 +29151,145 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>#12 Oriol Aby Tascón Marquié</t>
+          <t>#9 Eduard Illa Martinez</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="AG9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI9" s="2" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AK9" s="2" t="n">
-        <v>11.88</v>
-      </c>
       <c r="AL9" s="2" t="n">
-        <v>68.18181818181817</v>
+        <v>30</v>
       </c>
       <c r="AM9" s="2" t="n">
-        <v>71.54882154882154</v>
+        <v>30</v>
       </c>
       <c r="AN9" s="2" t="n">
-        <v>1.430976430976431</v>
+        <v>0.6</v>
       </c>
       <c r="AO9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>0.1818181818181818</v>
+        <v>0</v>
       </c>
       <c r="AQ9" s="2" t="n">
-        <v>35.25062558265051</v>
+        <v>22.38441903780496</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AT9" s="2" t="n">
-        <v>45.45454545454545</v>
+        <v>20</v>
       </c>
       <c r="AU9" s="2" t="n">
         <v>0</v>
@@ -29298,191 +29298,191 @@
         <v>50</v>
       </c>
       <c r="AW9" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>#15 Albert Sitjes Lozano</t>
+          <t>#10 Xavi Maixenchs Bobe</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="n">
+      <c r="S10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="AH10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="W10" s="2" t="n">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AI10" s="2" t="n">
-        <v>0</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>29:34</t>
+          <t>27:05</t>
         </is>
       </c>
       <c r="AK10" s="2" t="n">
-        <v>10.64</v>
+        <v>11.32</v>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="AM10" s="2" t="n">
-        <v>28.19548872180451</v>
+        <v>66.25441696113073</v>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.5154639175257731</v>
+        <v>1.217532467532467</v>
       </c>
       <c r="AO10" s="2" t="n">
-        <v>8.59106529209622</v>
+        <v>8.116883116883116</v>
       </c>
       <c r="AP10" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="2" t="n">
-        <v>17.83385480663263</v>
+        <v>21.3153667346136</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AT10" s="2" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="AU10" s="2" t="n">
-        <v>14.28571428571428</v>
+        <v>0</v>
       </c>
       <c r="AV10" s="2" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="AW10" s="2" t="n">
-        <v>66.66666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>#44 Gonzalo Fernando Badal</t>
+          <t>#15 Joan Odena Massaguer</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>0</v>
@@ -29497,19 +29497,19 @@
         <v>0</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S11" s="2" t="n">
         <v>0</v>
@@ -29518,99 +29518,99 @@
         <v>2</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>100</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="AD11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AG11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI11" s="2" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>30:50</t>
+          <t>30:16</t>
         </is>
       </c>
       <c r="AK11" s="2" t="n">
-        <v>11.2</v>
+        <v>15.76</v>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>66.66666666666666</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="AM11" s="2" t="n">
-        <v>66.96428571428572</v>
+        <v>53.93401015228426</v>
       </c>
       <c r="AN11" s="2" t="n">
-        <v>1.339285714285714</v>
+        <v>1.014319809069212</v>
       </c>
       <c r="AO11" s="2" t="n">
-        <v>0</v>
+        <v>5.966587112171839</v>
       </c>
       <c r="AP11" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ11" s="2" t="n">
-        <v>16.4547828727604</v>
+        <v>25.94738744606032</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT11" s="2" t="n">
-        <v>66.66666666666666</v>
+        <v>50</v>
       </c>
       <c r="AU11" s="2" t="n">
-        <v>66.66666666666666</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="AV11" s="2" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="AW11" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>#77 Adrià Ordobàs Bengado</t>
+          <t>#17 Bru Postigo Camprubi</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -29620,22 +29620,22 @@
         <v>6</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0</v>
@@ -29662,7 +29662,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="S12" s="2" t="n">
         <v>0</v>
@@ -29671,13 +29671,13 @@
         <v>0</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X12" s="2" t="n">
         <v>0</v>
@@ -29698,91 +29698,91 @@
         <v>0</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AI12" s="2" t="n">
-        <v>16.66666666666666</v>
+        <v>50</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AK12" s="2" t="n">
-        <v>9</v>
+        <v>4.44</v>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="AM12" s="2" t="n">
-        <v>33.33333333333333</v>
+        <v>67.56756756756756</v>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="AO12" s="2" t="n">
-        <v>25</v>
+        <v>40.32258064516129</v>
       </c>
       <c r="AP12" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AQ12" s="2" t="n">
-        <v>38.96741975756112</v>
+        <v>17.8934420459738</v>
       </c>
       <c r="AR12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
         <v>2</v>
       </c>
       <c r="AT12" s="2" t="n">
-        <v>22.22222222222222</v>
+        <v>50</v>
       </c>
       <c r="AU12" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AV12" s="2" t="n">
-        <v>22.22222222222222</v>
+        <v>50</v>
       </c>
       <c r="AW12" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>#87 Javier Vicente Nieto</t>
+          <t>#28 Iago Carbajo Aubeso</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>0</v>
@@ -29809,28 +29809,28 @@
         <v>1</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X13" s="2" t="n">
         <v>0</v>
@@ -29851,63 +29851,63 @@
         <v>0</v>
       </c>
       <c r="AD13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AG13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI13" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AK13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL13" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM13" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN13" s="2" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="AO13" s="2" t="n">
-        <v>11.11111111111111</v>
-      </c>
       <c r="AP13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" s="2" t="n">
-        <v>20.45300815452256</v>
+        <v>7.831429056123406</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT13" s="2" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="AU13" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AV13" s="2" t="n">
-        <v>28.57142857142857</v>
+        <v>0</v>
       </c>
       <c r="AW13" s="2" t="n">
         <v>0</v>

--- a/data/raw/Copa_2026_2027/aggregate/aggregated_game_stats_with_defense.xlsx
+++ b/data/raw/Copa_2026_2027/aggregate/aggregated_game_stats_with_defense.xlsx
@@ -15284,8 +15284,12 @@
       <c r="D2" s="2" t="n">
         <v>39.34426229508197</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" s="2" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>42.86</v>
+      </c>
       <c r="G2" s="2" t="n">
         <v>0.2295081967213115</v>
       </c>
@@ -15357,10 +15361,10 @@
         <v>42.02898550724638</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30.345</v>
+        <v>30.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46.93</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.2463768115942029</v>
@@ -15432,8 +15436,12 @@
       <c r="D4" s="2" t="n">
         <v>39.74358974358974</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" s="2" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>42.86</v>
+      </c>
       <c r="G4" s="2" t="n">
         <v>0.2051282051282051</v>
       </c>
@@ -15505,10 +15513,10 @@
         <v>37.34939759036144</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>26.82</v>
+        <v>20.43</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>31.65</v>
+        <v>43.86</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.08433734939759036</v>
@@ -15581,10 +15589,10 @@
         <v>29.23076923076923</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>28.68</v>
+        <v>25.65</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>34.97</v>
+        <v>27.08</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0.1538461538461539</v>
@@ -15656,8 +15664,12 @@
       <c r="D7" s="2" t="n">
         <v>48.21428571428572</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" s="2" t="n">
+        <v>33.21</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>19.44</v>
+      </c>
       <c r="G7" s="2" t="n">
         <v>0.1964285714285714</v>
       </c>
@@ -15729,10 +15741,10 @@
         <v>51.75438596491229</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33.095</v>
+        <v>30.59</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>43.38</v>
+        <v>39.39</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.2807017543859649</v>
@@ -15804,8 +15816,12 @@
       <c r="D9" s="2" t="n">
         <v>30.88235294117647</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" s="2" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>43.86</v>
+      </c>
       <c r="G9" s="2" t="n">
         <v>0.25</v>
       </c>
@@ -15877,10 +15893,10 @@
         <v>52.66666666666666</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>31.715</v>
+        <v>30.74</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>33.665</v>
+        <v>44</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.1733333333333333</v>
@@ -15953,10 +15969,10 @@
         <v>35.11904761904761</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>23.965</v>
+        <v>23.35</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>43.095</v>
+        <v>43.33</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.119047619047619</v>
@@ -16029,10 +16045,10 @@
         <v>45.65217391304348</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>25.365</v>
+        <v>25.23</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>29.03</v>
+        <v>35.56</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.2318840579710145</v>
@@ -16104,8 +16120,12 @@
       <c r="D13" s="2" t="n">
         <v>51.51515151515152</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" s="2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G13" s="2" t="n">
         <v>0.1060606060606061</v>
       </c>
@@ -16176,8 +16196,12 @@
       <c r="D14" s="2" t="n">
         <v>45.76271186440678</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" s="2" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>47.37</v>
+      </c>
       <c r="G14" s="2" t="n">
         <v>0.2033898305084746</v>
       </c>
@@ -16248,8 +16272,12 @@
       <c r="D15" s="2" t="n">
         <v>54.23728813559322</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="E15" s="2" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>23.33</v>
+      </c>
       <c r="G15" s="2" t="n">
         <v>0.288135593220339</v>
       </c>

--- a/data/raw/Copa_2026_2027/aggregate/aggregated_game_stats_with_defense.xlsx
+++ b/data/raw/Copa_2026_2027/aggregate/aggregated_game_stats_with_defense.xlsx
@@ -31821,7 +31821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33149,70 +33149,70 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>4.666666666666667</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="P9" s="1" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Q9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="1" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="T9" s="1" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="U9" s="1" t="n">
-        <v>2.666666666666667</v>
-      </c>
       <c r="V9" s="1" t="n">
-        <v>5.333333333333333</v>
+        <v>5.75</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>50</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>0</v>
@@ -33224,13 +33224,13 @@
         <v>0</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.25</v>
       </c>
       <c r="AC9" s="1" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AD9" s="1" t="n">
         <v>0</v>
@@ -33252,78 +33252,78 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>8.053333333333333</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>50</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>49.66887417218543</v>
+        <v>52.98913043478262</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>0.823045267489712</v>
+        <v>0.9112149532710281</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>17.14677640603567</v>
+        <v>14.01869158878505</v>
       </c>
       <c r="AP9" s="1" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="AQ9" s="1" t="n">
-        <v>18.26943177414965</v>
+        <v>20.09953797533571</v>
       </c>
       <c r="AR9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AT9" s="1" t="n">
-        <v>50</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="AU9" s="1" t="n">
-        <v>50</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="AV9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AW9" s="1" t="n">
-        <v>42.85714285714285</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>#7 Jose López Martínez</t>
+          <t>#9 Eduard Illa Martinez</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>10</v>
+        <v>1.75</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>0</v>
@@ -33338,145 +33338,145 @@
         <v>0</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>7</v>
+        <v>1.25</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>57.14285714285714</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="1" t="n">
-        <v>66.66666666666666</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="1" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE10" s="1" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>12.64</v>
+        <v>4.72</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>60</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>59.33544303797468</v>
+        <v>47.66949152542373</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>1.099706744868035</v>
+        <v>0.9054325955734407</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>7.331378299120233</v>
+        <v>5.030181086519115</v>
       </c>
       <c r="AP10" s="1" t="n">
-        <v>0.3</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="AQ10" s="1" t="n">
-        <v>25.57691381933813</v>
+        <v>16.71766385674717</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="AT10" s="1" t="n">
-        <v>60</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AU10" s="1" t="n">
-        <v>60</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AV10" s="1" t="n">
-        <v>0</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AW10" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>#9 Eduard Illa Martinez</t>
+          <t>#10 Xavi Maixenchs Bobe</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>1.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>2.75</v>
+        <v>6</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.5</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>0</v>
@@ -33491,264 +33491,264 @@
         <v>0</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.25</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>0.25</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>0.75</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="Q11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>1.25</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>1.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="1" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="X11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE11" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF11" s="1" t="n">
-        <v>50</v>
-      </c>
       <c r="AG11" s="1" t="n">
-        <v>0.75</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="AI11" s="1" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>4.72</v>
+        <v>7.693333333333334</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>44.44444444444444</v>
+        <v>45</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>47.66949152542373</v>
+        <v>38.9948006932409</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.9054325955734407</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>5.030181086519115</v>
+        <v>17.8062678062678</v>
       </c>
       <c r="AP11" s="1" t="n">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="AQ11" s="1" t="n">
-        <v>16.71766385674717</v>
+        <v>25.00929492744666</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AT11" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="1" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="AU11" s="1" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="AV11" s="1" t="n">
-        <v>36.36363636363637</v>
-      </c>
       <c r="AW11" s="1" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>#10 Xavi Maixenchs Bobe</t>
+          <t>#12 Marc Latorre Rams</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="S12" s="1" t="n">
+      <c r="U12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="AK12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="W12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="1" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AE12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="1" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="AG12" s="1" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AH12" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI12" s="1" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AK12" s="1" t="n">
-        <v>7.693333333333334</v>
-      </c>
       <c r="AL12" s="1" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>38.9948006932409</v>
+        <v>50</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.641025641025641</v>
+        <v>1</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>17.8062678062678</v>
+        <v>0</v>
       </c>
       <c r="AP12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" s="1" t="n">
-        <v>25.00929492744666</v>
+        <v>28.3577368705946</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="AS12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT12" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AU12" s="1" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AV12" s="1" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="AW12" s="1" t="n">
         <v>0</v>
@@ -33757,185 +33757,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>#12 Marc Latorre Rams</t>
+          <t>#15 Joan Odena Massaguer</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="X13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="AC13" s="1" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AD13" s="1" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE13" s="1" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>0</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>03:07</t>
+          <t>32:04</t>
         </is>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>2</v>
+        <v>15.05</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>50</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>50</v>
+        <v>51.49501661129568</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>1</v>
+        <v>0.950920245398773</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0</v>
+        <v>7.668711656441718</v>
       </c>
       <c r="AP13" s="1" t="n">
-        <v>0</v>
+        <v>0.03448275862068965</v>
       </c>
       <c r="AQ13" s="1" t="n">
-        <v>28.3577368705946</v>
+        <v>22.46289442704246</v>
       </c>
       <c r="AR13" t="n">
-        <v>2</v>
+        <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1</v>
+        <v>6.25</v>
       </c>
       <c r="AT13" s="1" t="n">
-        <v>50</v>
+        <v>43.10344827586206</v>
       </c>
       <c r="AU13" s="1" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AV13" s="1" t="n">
-        <v>0</v>
+        <v>30.3030303030303</v>
       </c>
       <c r="AW13" s="1" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>#15 Joan Odena Massaguer</t>
+          <t>#17 Bru Postigo Camprubi</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>15.5</v>
+        <v>3.5</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>3.75</v>
+        <v>0.75</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>6.25</v>
+        <v>2.75</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>8.25</v>
+        <v>0.75</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>0</v>
@@ -33950,419 +33950,266 @@
         <v>0</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="Q14" s="1" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>5.25</v>
+        <v>0.5</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="V14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI14" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>32.14285714285715</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>40.98360655737706</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>0.6972111553784861</v>
+      </c>
+      <c r="AO14" s="1" t="n">
+        <v>14.9402390438247</v>
+      </c>
+      <c r="AP14" s="1" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AQ14" s="1" t="n">
+        <v>14.79329919972324</v>
+      </c>
+      <c r="AR14" t="n">
         <v>3.5</v>
       </c>
-      <c r="W14" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="X14" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y14" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Z14" s="1" t="n">
-        <v>66.66666666666666</v>
-      </c>
-      <c r="AA14" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB14" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC14" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="AD14" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE14" s="1" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF14" s="1" t="n">
-        <v>9.090909090909092</v>
-      </c>
-      <c r="AG14" s="1" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH14" s="1" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI14" s="1" t="n">
-        <v>40.90909090909091</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>32:04</t>
-        </is>
-      </c>
-      <c r="AK14" s="1" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="AL14" s="1" t="n">
-        <v>51.72413793103448</v>
-      </c>
-      <c r="AM14" s="1" t="n">
-        <v>51.49501661129568</v>
-      </c>
-      <c r="AN14" s="1" t="n">
-        <v>0.950920245398773</v>
-      </c>
-      <c r="AO14" s="1" t="n">
-        <v>7.668711656441718</v>
-      </c>
-      <c r="AP14" s="1" t="n">
-        <v>0.03448275862068965</v>
-      </c>
-      <c r="AQ14" s="1" t="n">
-        <v>22.46289442704246</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AS14" t="n">
-        <v>6.25</v>
+        <v>1</v>
       </c>
       <c r="AT14" s="1" t="n">
-        <v>43.10344827586206</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AU14" s="1" t="n">
-        <v>60</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AV14" s="1" t="n">
-        <v>30.3030303030303</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="AW14" s="1" t="n">
-        <v>40</v>
+        <v>71.42857142857143</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>#17 Bru Postigo Camprubi</t>
+          <t>#28 Iago Carbajo Aubeso</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>0.75</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="F15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="I15" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="Q15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V15" s="1" t="n">
         <v>1.25</v>
       </c>
-      <c r="I15" s="1" t="n">
+      <c r="W15" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AK15" s="1" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL15" s="1" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="AM15" s="1" t="n">
+        <v>44.41624365482234</v>
+      </c>
+      <c r="AN15" s="1" t="n">
+        <v>0.5892255892255893</v>
+      </c>
+      <c r="AO15" s="1" t="n">
+        <v>33.67003367003367</v>
+      </c>
+      <c r="AP15" s="1" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AQ15" s="1" t="n">
+        <v>11.277911550705</v>
+      </c>
+      <c r="AR15" t="n">
         <v>1.75</v>
       </c>
-      <c r="J15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O15" s="1" t="n">
+      <c r="AS15" t="n">
         <v>0.75</v>
       </c>
-      <c r="P15" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T15" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U15" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V15" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="W15" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="X15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AB15" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AC15" s="1" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="AD15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AH15" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI15" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AK15" s="1" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="AL15" s="1" t="n">
-        <v>32.14285714285715</v>
-      </c>
-      <c r="AM15" s="1" t="n">
-        <v>40.98360655737706</v>
-      </c>
-      <c r="AN15" s="1" t="n">
-        <v>0.6972111553784861</v>
-      </c>
-      <c r="AO15" s="1" t="n">
-        <v>14.9402390438247</v>
-      </c>
-      <c r="AP15" s="1" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="AQ15" s="1" t="n">
-        <v>14.79329919972324</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1</v>
-      </c>
       <c r="AT15" s="1" t="n">
-        <v>28.57142857142857</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AU15" s="1" t="n">
-        <v>27.27272727272727</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AV15" s="1" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="AW15" s="1" t="n">
-        <v>71.42857142857143</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>#28 Iago Carbajo Aubeso</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="S16" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W16" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="X16" s="1" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y16" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z16" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AK16" s="1" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AL16" s="1" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="AM16" s="1" t="n">
-        <v>44.41624365482234</v>
-      </c>
-      <c r="AN16" s="1" t="n">
-        <v>0.5892255892255893</v>
-      </c>
-      <c r="AO16" s="1" t="n">
-        <v>33.67003367003367</v>
-      </c>
-      <c r="AP16" s="1" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="AQ16" s="1" t="n">
-        <v>11.277911550705</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AT16" s="1" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="AU16" s="1" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="AV16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" s="1" t="n">
         <v>50</v>
       </c>
     </row>
